--- a/analyses/data/LocationData.xlsx
+++ b/analyses/data/LocationData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexikeene/Documents/Research/diverse_collections/github/analyses/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF2A53D-45C9-F04E-95B7-9C06AF1A5CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BF9B65-B1B9-904C-A766-DEE2990095AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7420" yWindow="760" windowWidth="14700" windowHeight="15860" xr2:uid="{1D392CE1-C1B7-5B4F-A5CD-CD91EAEAFFF0}"/>
   </bookViews>
@@ -35,10 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
-  <si>
-    <t>number</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>state</t>
   </si>
@@ -463,228 +460,198 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED4201E3-4104-2747-B819-36548A90AB07}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>40.534689</v>
+      </c>
+      <c r="D2">
+        <v>-105.09463599999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>1020</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>40.595027000000002</v>
+      </c>
+      <c r="D3">
+        <v>-105.103854</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>40.580078</v>
+      </c>
+      <c r="D4">
+        <v>-105.083673</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>40.551983</v>
+      </c>
+      <c r="D5">
+        <v>-105.04247700000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>40.592587000000002</v>
+      </c>
+      <c r="D6">
+        <v>-105.068291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>40.572721000000001</v>
+      </c>
+      <c r="D7">
+        <v>-105.118279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>40.575502</v>
+      </c>
+      <c r="D8">
+        <v>-105.144156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="D2">
-        <v>40.534689</v>
-      </c>
-      <c r="E2">
-        <v>-105.09463599999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>1428</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>40.595027000000002</v>
-      </c>
-      <c r="E3">
-        <v>-105.103854</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>417</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4">
-        <v>40.580078</v>
-      </c>
-      <c r="E4">
-        <v>-105.083673</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>40.551983</v>
-      </c>
-      <c r="E5">
-        <v>-105.04247700000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>500</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>40.592587000000002</v>
-      </c>
-      <c r="E6">
-        <v>-105.068291</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>1037</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7">
-        <v>40.572721000000001</v>
-      </c>
-      <c r="E7">
-        <v>-105.118279</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8">
-        <v>40.575502</v>
-      </c>
-      <c r="E8">
-        <v>-105.144156</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>40.410659000000003</v>
+      </c>
+      <c r="D9">
+        <v>-105.101088</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>40.525444999999998</v>
+      </c>
+      <c r="D10">
+        <v>-105.07343899999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B9">
-        <v>1705</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9">
-        <v>40.410659000000003</v>
-      </c>
-      <c r="E9">
-        <v>-105.101088</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10">
-        <v>40.525444999999998</v>
-      </c>
-      <c r="E10">
-        <v>-105.07343899999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="B11">
-        <v>541</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="C11">
+        <v>40.818320999999997</v>
+      </c>
+      <c r="D11">
+        <v>-81.932565999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="D11">
-        <v>40.818320999999997</v>
-      </c>
-      <c r="E11">
-        <v>-81.932565999999994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="B12">
-        <v>660</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="C12">
+        <v>40.822166000000003</v>
+      </c>
+      <c r="D12">
+        <v>-77.889156999999997</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="D12">
-        <v>40.822166000000003</v>
-      </c>
-      <c r="E12">
-        <v>-77.889156999999997</v>
-      </c>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="B13">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
+      <c r="C13">
+        <v>44.529775000000001</v>
       </c>
       <c r="D13">
-        <v>44.529775000000001</v>
-      </c>
-      <c r="E13">
         <v>-69.630373000000006</v>
       </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="16" spans="1:8" ht="18" x14ac:dyDescent="0.2">
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E17" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D17" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
